--- a/data/gravel/Ventum GS1 2025.xlsx
+++ b/data/gravel/Ventum GS1 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77FA659-BFC5-EA46-9D61-C04CA27693C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FD6F00-8D48-9C4C-ABF8-15BA2A307779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25320" yWindow="-16040" windowWidth="25560" windowHeight="15020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -564,6 +564,9 @@
       </rPr>
       <t> FORK OFFSET (Not Shown) </t>
     </r>
+  </si>
+  <si>
+    <t>https://cdn11.bigcommerce.com/s-socd7uniqk/images/stencil/original/image-manager/v3-gs1-ecom-redsplatter-sram-red-xplr-1.jpg?t=1747845588</t>
   </si>
 </sst>
 </file>
@@ -976,6 +979,11 @@
         <v>91</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+    </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>

--- a/data/gravel/Ventum GS1 2025.xlsx
+++ b/data/gravel/Ventum GS1 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FD6F00-8D48-9C4C-ABF8-15BA2A307779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CBD2FF-3397-5246-8CC6-02F3A29FA2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13300" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -336,9 +336,6 @@
   </si>
   <si>
     <t>no</t>
-  </si>
-  <si>
-    <t>usd</t>
   </si>
   <si>
     <r>
@@ -567,6 +564,15 @@
   </si>
   <si>
     <t>https://cdn11.bigcommerce.com/s-socd7uniqk/images/stencil/original/image-manager/v3-gs1-ecom-redsplatter-sram-red-xplr-1.jpg?t=1747845588</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Heber City, Utah, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -933,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -981,7 +987,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1031,7 +1037,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" s="5">
         <v>506</v>
@@ -1058,7 +1064,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" s="5">
         <v>369</v>
@@ -1085,7 +1091,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="5">
         <v>90</v>
@@ -1112,7 +1118,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" s="5">
         <v>420</v>
@@ -1139,7 +1145,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C13" s="5">
         <v>594</v>
@@ -1166,7 +1172,7 @@
         <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="5">
         <v>1004</v>
@@ -1193,7 +1199,7 @@
         <v>22</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="5">
         <v>70</v>
@@ -1220,7 +1226,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" s="5">
         <v>74</v>
@@ -1247,7 +1253,7 @@
         <v>24</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" s="5">
         <v>69</v>
@@ -1274,7 +1280,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="5">
         <v>514</v>
@@ -1301,7 +1307,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" s="5">
         <v>485</v>
@@ -1328,7 +1334,7 @@
         <v>27</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" s="5">
         <v>778</v>
@@ -1357,7 +1363,7 @@
         <v>99</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C21" s="5">
         <v>86</v>
@@ -1386,7 +1392,7 @@
         <v>28</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" s="5">
         <v>395</v>
@@ -1413,7 +1419,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23" s="5">
         <v>50</v>
@@ -2304,7 +2310,7 @@
         <v>84</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -2314,6 +2320,14 @@
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
     </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>117</v>
+      </c>
+      <c r="B75" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Ventum GS1 2025.xlsx
+++ b/data/gravel/Ventum GS1 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CBD2FF-3397-5246-8CC6-02F3A29FA2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F127D85-40C2-1048-B9EE-61DC689E6ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13300" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -59,9 +59,6 @@
     <t>data_range</t>
   </si>
   <si>
-    <t>a8:h34</t>
-  </si>
-  <si>
     <t>frame_size</t>
   </si>
   <si>
@@ -318,12 +315,6 @@
   </si>
   <si>
     <t>integrated</t>
-  </si>
-  <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
   </si>
   <si>
     <t>FRAME SIZE</t>
@@ -573,6 +564,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>a8:h32</t>
   </si>
 </sst>
 </file>
@@ -939,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -982,12 +976,12 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -995,7 +989,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1007,37 +1001,37 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C9" s="5">
         <v>506</v>
@@ -1061,10 +1055,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C10" s="5">
         <v>369</v>
@@ -1088,10 +1082,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C11" s="5">
         <v>90</v>
@@ -1115,10 +1109,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C12" s="5">
         <v>420</v>
@@ -1142,10 +1136,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C13" s="5">
         <v>594</v>
@@ -1169,10 +1163,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C14" s="5">
         <v>1004</v>
@@ -1196,10 +1190,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="5">
         <v>70</v>
@@ -1223,10 +1217,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C16" s="5">
         <v>74</v>
@@ -1250,10 +1244,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C17" s="5">
         <v>69</v>
@@ -1277,10 +1271,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C18" s="5">
         <v>514</v>
@@ -1304,10 +1298,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C19" s="5">
         <v>485</v>
@@ -1331,10 +1325,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C20" s="5">
         <v>778</v>
@@ -1355,15 +1349,15 @@
         <v>874</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C21" s="5">
         <v>86</v>
@@ -1384,15 +1378,15 @@
         <v>62</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C22" s="5">
         <v>395</v>
@@ -1416,10 +1410,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C23" s="5">
         <v>50</v>
@@ -1443,10 +1437,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C24" s="2">
         <v>165</v>
@@ -1470,10 +1464,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C25" s="5">
         <v>380</v>
@@ -1497,10 +1491,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C26" s="2">
         <v>90</v>
@@ -1524,7 +1518,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1537,10 +1531,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="C28" s="2">
         <v>700</v>
@@ -1564,10 +1558,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C29" s="2">
         <v>50</v>
@@ -1591,10 +1585,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="C30" s="2">
         <v>50</v>
@@ -1618,188 +1612,156 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C31" s="6">
-        <f>C33</f>
+        <f>C33*2.54</f>
         <v>149.86000000000001</v>
       </c>
       <c r="D31" s="6">
-        <f>AVERAGE(D33,C34)</f>
+        <f>D33*2.54</f>
         <v>162.56</v>
       </c>
       <c r="E31" s="6">
-        <f t="shared" ref="E31:H31" si="0">AVERAGE(E33,D34)</f>
+        <f>E33*2.54</f>
         <v>170.18</v>
       </c>
       <c r="F31" s="6">
-        <f t="shared" si="0"/>
-        <v>179.07</v>
+        <f>F33*2.54</f>
+        <v>177.8</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="0"/>
+        <f>G33*2.54</f>
         <v>185.42000000000002</v>
       </c>
       <c r="H31" s="6">
-        <f t="shared" si="0"/>
-        <v>191.76999999999998</v>
+        <f>H33*2.54</f>
+        <v>193.04</v>
       </c>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C32" s="6">
-        <f>D31</f>
+        <f>C34*2.54</f>
         <v>162.56</v>
       </c>
       <c r="D32" s="6">
-        <f t="shared" ref="D32:G32" si="1">E31</f>
+        <f>D34*2.54</f>
         <v>170.18</v>
       </c>
       <c r="E32" s="6">
-        <f t="shared" si="1"/>
-        <v>179.07</v>
+        <f>E34*2.54</f>
+        <v>180.34</v>
       </c>
       <c r="F32" s="6">
-        <f t="shared" si="1"/>
+        <f>F34*2.54</f>
         <v>185.42000000000002</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="1"/>
-        <v>191.76999999999998</v>
+        <f>G34*2.54</f>
+        <v>190.5</v>
       </c>
       <c r="H32" s="6">
-        <f>H34</f>
+        <f>H34*2.54</f>
         <v>198.12</v>
       </c>
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="6">
-        <f>C35*2.54</f>
-        <v>149.86000000000001</v>
-      </c>
-      <c r="D33" s="6">
-        <f t="shared" ref="D33:G34" si="2">D35*2.54</f>
-        <v>162.56</v>
-      </c>
-      <c r="E33" s="6">
-        <f t="shared" si="2"/>
-        <v>170.18</v>
-      </c>
-      <c r="F33" s="6">
-        <f t="shared" si="2"/>
-        <v>177.8</v>
-      </c>
-      <c r="G33" s="6">
-        <f t="shared" si="2"/>
-        <v>185.42000000000002</v>
-      </c>
-      <c r="H33" s="6">
-        <f>H35*2.54</f>
-        <v>193.04</v>
+      <c r="C33" s="2">
+        <v>59</v>
+      </c>
+      <c r="D33" s="2">
+        <v>64</v>
+      </c>
+      <c r="E33" s="2">
+        <v>67</v>
+      </c>
+      <c r="F33" s="2">
+        <v>70</v>
+      </c>
+      <c r="G33" s="2">
+        <v>73</v>
+      </c>
+      <c r="H33" s="2">
+        <v>76</v>
       </c>
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="6">
-        <f>C36*2.54</f>
-        <v>162.56</v>
-      </c>
-      <c r="D34" s="6">
-        <f t="shared" si="2"/>
-        <v>170.18</v>
-      </c>
-      <c r="E34" s="6">
-        <f t="shared" si="2"/>
-        <v>180.34</v>
-      </c>
-      <c r="F34" s="6">
-        <f t="shared" si="2"/>
-        <v>185.42000000000002</v>
-      </c>
-      <c r="G34" s="6">
-        <f t="shared" si="2"/>
-        <v>190.5</v>
-      </c>
-      <c r="H34" s="6">
-        <f>H36*2.54</f>
-        <v>198.12</v>
+        <v>46</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="2">
+        <v>64</v>
+      </c>
+      <c r="D34" s="2">
+        <v>67</v>
+      </c>
+      <c r="E34" s="2">
+        <v>71</v>
+      </c>
+      <c r="F34" s="2">
+        <v>73</v>
+      </c>
+      <c r="G34" s="2">
+        <v>75</v>
+      </c>
+      <c r="H34" s="2">
+        <v>78</v>
       </c>
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2">
-        <v>59</v>
-      </c>
-      <c r="D35" s="2">
-        <v>64</v>
-      </c>
-      <c r="E35" s="2">
-        <v>67</v>
-      </c>
-      <c r="F35" s="2">
-        <v>70</v>
-      </c>
-      <c r="G35" s="2">
-        <v>73</v>
-      </c>
-      <c r="H35" s="2">
-        <v>76</v>
-      </c>
+      <c r="A35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="2">
-        <v>64</v>
-      </c>
-      <c r="D36" s="2">
-        <v>67</v>
-      </c>
-      <c r="E36" s="2">
-        <v>71</v>
-      </c>
-      <c r="F36" s="2">
-        <v>73</v>
-      </c>
-      <c r="G36" s="2">
-        <v>75</v>
-      </c>
-      <c r="H36" s="2">
-        <v>78</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1811,10 +1773,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -1826,10 +1788,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1841,11 +1803,9 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -1856,10 +1816,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>92</v>
+        <v>52</v>
+      </c>
+      <c r="B41" s="2">
+        <v>50</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -1871,7 +1831,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1884,11 +1844,9 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -1899,7 +1857,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -1912,7 +1870,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1925,7 +1883,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1938,7 +1896,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -1951,7 +1909,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -1964,9 +1922,11 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B49" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1977,7 +1937,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -1990,11 +1950,9 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -2005,9 +1963,11 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -2018,7 +1978,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2031,11 +1991,9 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -2046,7 +2004,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2059,7 +2017,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2072,7 +2030,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2085,9 +2043,11 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B58" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -2098,7 +2058,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2111,11 +2071,9 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>94</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -2126,9 +2084,11 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B61" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -2139,9 +2099,11 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B62" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="B62" s="2">
+        <v>2</v>
+      </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -2152,10 +2114,10 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -2167,10 +2129,10 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B64" s="2">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -2182,11 +2144,9 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>100</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
@@ -2197,11 +2157,9 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -2212,7 +2170,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2225,7 +2183,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -2238,9 +2196,11 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B69" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="B69" s="2">
+        <v>2899</v>
+      </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -2251,9 +2211,11 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B70" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="B70" s="2">
+        <v>3499</v>
+      </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -2264,11 +2226,9 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B71" s="2">
-        <v>2899</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
@@ -2279,10 +2239,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="2">
-        <v>3499</v>
+        <v>83</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -2293,39 +2253,11 @@
       <c r="I72" s="2"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>117</v>
-      </c>
-      <c r="B75" t="s">
-        <v>118</v>
+      <c r="A73" t="s">
+        <v>114</v>
+      </c>
+      <c r="B73" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Ventum GS1 2025.xlsx
+++ b/data/gravel/Ventum GS1 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F127D85-40C2-1048-B9EE-61DC689E6ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDC2624-833A-D145-AC96-854D45BD018D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -567,6 +567,24 @@
   </si>
   <si>
     <t>a8:h32</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -933,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1618,27 +1636,27 @@
         <v>43</v>
       </c>
       <c r="C31" s="6">
-        <f>C33*2.54</f>
+        <f t="shared" ref="C31:H32" si="0">C33*2.54</f>
         <v>149.86000000000001</v>
       </c>
       <c r="D31" s="6">
-        <f>D33*2.54</f>
+        <f t="shared" si="0"/>
         <v>162.56</v>
       </c>
       <c r="E31" s="6">
-        <f>E33*2.54</f>
+        <f t="shared" si="0"/>
         <v>170.18</v>
       </c>
       <c r="F31" s="6">
-        <f>F33*2.54</f>
+        <f t="shared" si="0"/>
         <v>177.8</v>
       </c>
       <c r="G31" s="6">
-        <f>G33*2.54</f>
+        <f t="shared" si="0"/>
         <v>185.42000000000002</v>
       </c>
       <c r="H31" s="6">
-        <f>H33*2.54</f>
+        <f t="shared" si="0"/>
         <v>193.04</v>
       </c>
       <c r="I31" s="2"/>
@@ -1651,27 +1669,27 @@
         <v>45</v>
       </c>
       <c r="C32" s="6">
-        <f>C34*2.54</f>
+        <f t="shared" si="0"/>
         <v>162.56</v>
       </c>
       <c r="D32" s="6">
-        <f>D34*2.54</f>
+        <f t="shared" si="0"/>
         <v>170.18</v>
       </c>
       <c r="E32" s="6">
-        <f>E34*2.54</f>
+        <f t="shared" si="0"/>
         <v>180.34</v>
       </c>
       <c r="F32" s="6">
-        <f>F34*2.54</f>
+        <f t="shared" si="0"/>
         <v>185.42000000000002</v>
       </c>
       <c r="G32" s="6">
-        <f>G34*2.54</f>
+        <f t="shared" si="0"/>
         <v>190.5</v>
       </c>
       <c r="H32" s="6">
-        <f>H34*2.54</f>
+        <f t="shared" si="0"/>
         <v>198.12</v>
       </c>
       <c r="I32" s="2"/>
@@ -1922,11 +1940,9 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1937,7 +1953,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -1950,7 +1966,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -1963,11 +1979,9 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>91</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -1978,7 +1992,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -1991,7 +2005,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2004,9 +2018,11 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
@@ -2017,7 +2033,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2030,7 +2046,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2043,10 +2059,10 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -2058,7 +2074,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2071,7 +2087,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2084,11 +2100,9 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>97</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -2099,11 +2113,9 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B62" s="2">
-        <v>2</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -2114,11 +2126,9 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>97</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -2129,10 +2139,10 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -2144,7 +2154,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2157,7 +2167,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2170,9 +2180,11 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B67" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -2183,9 +2195,11 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="B68" s="2">
+        <v>2</v>
+      </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
@@ -2196,10 +2210,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B69" s="2">
-        <v>2899</v>
+        <v>74</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2211,10 +2225,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B70" s="2">
-        <v>3499</v>
+        <v>75</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -2226,7 +2240,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -2239,11 +2253,9 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>116</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -2253,10 +2265,94 @@
       <c r="I72" s="2"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="2">
+        <v>2899</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="2">
+        <v>3499</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>114</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>115</v>
       </c>
     </row>
